--- a/docs/Illustration_UL/Exception prem testing.xlsx
+++ b/docs/Illustration_UL/Exception prem testing.xlsx
@@ -47,7 +47,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -59,6 +59,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,22 +405,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y685"/>
+  <dimension ref="A1:AE685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.140625" customWidth="1" min="2" max="4"/>
-    <col width="26.140625" customWidth="1" min="5" max="6"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="27.85546875" customWidth="1" min="8" max="8"/>
-    <col width="19.42578125" customWidth="1" min="9" max="9"/>
-    <col width="18.85546875" customWidth="1" min="10" max="10"/>
-    <col width="14.140625" customWidth="1" min="13" max="13"/>
-    <col width="19.85546875" customWidth="1" min="14" max="14"/>
-    <col width="14.140625" customWidth="1" min="15" max="15"/>
-    <col width="13.85546875" customWidth="1" min="16" max="17"/>
-    <col width="9.42578125" bestFit="1" customWidth="1" min="18" max="18"/>
-    <col width="12.5703125" bestFit="1" customWidth="1" min="19" max="19"/>
-    <col width="11.5703125" customWidth="1" min="24" max="24"/>
+    <col width="26.140625" customWidth="1" min="5" max="7"/>
+    <col width="24.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="27.85546875" customWidth="1" min="9" max="9"/>
+    <col width="19.42578125" customWidth="1" min="10" max="10"/>
+    <col width="18.85546875" customWidth="1" min="11" max="11"/>
+    <col width="14.140625" customWidth="1" min="14" max="14"/>
+    <col width="19.85546875" customWidth="1" min="15" max="15"/>
+    <col width="14.140625" customWidth="1" min="16" max="16"/>
+    <col width="13.85546875" customWidth="1" min="17" max="20"/>
+    <col width="9.42578125" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="12.5703125" bestFit="1" customWidth="1" min="22" max="22"/>
+    <col width="11.5703125" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,97 +456,127 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Absolute Max AV</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Run Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Min Level Prem</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Exception Duration</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Current Duration</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MD Diff</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Loan Amount</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Exception Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Face Amount</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Issue date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Maturity Date</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Maturity Duration</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Maturity Age</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Issue Age</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Attained Age</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>GSP</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>GLP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AccumLP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PremTD</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>AccumWD</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Valuation Date</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Suspense Code</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Total Prem Paid</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Def Life Ins</t>
         </is>
       </c>
     </row>
@@ -571,65 +604,83 @@
       <c r="F2" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Except Prem Required</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>48.08</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="J2" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>27.24</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="8" t="n">
         <v>53153</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>48560</v>
       </c>
-      <c r="P2" s="8" t="n">
+      <c r="Q2" s="8" t="n">
         <v>31238</v>
       </c>
-      <c r="Q2" s="8" t="n">
+      <c r="R2" s="8" t="n">
         <v>64110</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="U2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="S2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="W2" s="4" t="n">
         <v>3071.67</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="X2" s="4" t="n">
         <v>283.2</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="Y2" s="4" t="n">
         <v>11956.34</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>7638.78</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>1440</v>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Monthly</t>
+      <c r="AB2" s="8" t="n">
+        <v>46183</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AD2" s="4" t="n">
+        <v>195594.53</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -657,56 +708,83 @@
       <c r="F3" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>bypass (LN)</t>
-        </is>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Except Prem Required</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>174.46</v>
       </c>
       <c r="J3" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>5574.81</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="8" t="n">
+        <v>53166</v>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="P3" s="8" t="n">
+      <c r="Q3" s="8" t="n">
         <v>31251</v>
       </c>
-      <c r="Q3" s="8" t="n">
+      <c r="R3" s="8" t="n">
         <v>56088</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="U3" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="V3" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>2519.75</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>201.6</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="Y3" s="4" t="n">
         <v>7663.08</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>6326.75</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>has loan 5,574.81</t>
+      <c r="AB3" s="8" t="n">
+        <v>46165</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>56455.24</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -741,59 +819,76 @@
           <t>Maturity</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="9" t="n">
+        <v>-352662.7</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>bypass (A)</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>27.42</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="4" t="n">
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="Q4" s="8" t="n">
         <v>40869</v>
       </c>
-      <c r="Q4" s="8" t="n">
+      <c r="R4" s="8" t="n">
         <v>75932</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="U4" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="V4" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="W4" s="4" t="n">
         <v>5001.37</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="X4" s="4" t="n">
         <v>393.48</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="Y4" s="4" t="n">
         <v>5902.95</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>5115.12</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>active shadow account (benefit type A)</t>
+      <c r="AB4" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -826,65 +921,83 @@
       <c r="F5" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Except Prem Required</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>71.19</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>46.71</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8" t="n">
         <v>64214</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="Q5" s="8" t="n">
         <v>41873</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="R5" s="8" t="n">
         <v>74745</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="U5" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="V5" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="W5" s="4" t="n">
         <v>11927.96</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="X5" s="4" t="n">
         <v>854.16</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="Y5" s="4" t="n">
         <v>10250.64</v>
       </c>
-      <c r="W5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>10650</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Monthly</t>
+      <c r="AB5" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="n">
+        <v>706519.58</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -919,65 +1032,85 @@
           <t>Maturity</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="9" t="n">
+        <v>300651.37</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Except Prem Required</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>255.87</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>95.34999999999999</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8" t="n">
         <v>58570</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="Q6" s="8" t="n">
         <v>43778</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="R6" s="8" t="n">
         <v>69711</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="U6" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="V6" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="W6" s="4" t="n">
         <v>31311.53</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="X6" s="4" t="n">
         <v>2880.24</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="Y6" s="4" t="n">
         <v>20162.31</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>12421.68</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="AA6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Monthly</t>
+      <c r="AB6" s="8" t="n">
+        <v>46151</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="n">
+        <v>2113980.41</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -1002,66 +1135,86 @@
           <t>EXEC-UL</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Except Prem Required</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>182.2</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>48.1</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8" t="n">
         <v>58558</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>90000</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="Q7" s="8" t="n">
         <v>42670</v>
       </c>
-      <c r="Q7" s="5" t="n">
+      <c r="R7" s="8" t="n">
         <v>68602</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="U7" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="V7" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="W7" s="4" t="n">
         <v>23092.92</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="X7" s="4" t="n">
         <v>2072.4</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="Y7" s="4" t="n">
         <v>20724.2</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>16122.05</v>
       </c>
-      <c r="X7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Monthly</t>
+      <c r="AB7" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>1246041.46</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -1091,60 +1244,84 @@
           <t>1U538229, 1U538329</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>76849.39</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Matured w/o Except Prem</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>99.12</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>76.7</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="Q8" s="8" t="n">
         <v>31113</v>
       </c>
-      <c r="Q8" s="5" t="n">
+      <c r="R8" s="8" t="n">
         <v>55585</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="U8" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="V8" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="W8" s="4" t="n">
         <v>9685.15</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="X8" s="4" t="n">
         <v>846.72</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="Y8" s="4" t="n">
         <v>35565.18</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>23095.21</v>
       </c>
-      <c r="X8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Monthly</t>
+      <c r="AB8" s="8" t="n">
+        <v>46180</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="n">
+        <v>53624.17</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -1169,66 +1346,86 @@
           <t>FPL83</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Except Prem Required</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>2924.98</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>152.46</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" t="n">
         <v>52971</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>120000</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="Q9" s="8" t="n">
         <v>31146</v>
       </c>
-      <c r="Q9" s="5" t="n">
+      <c r="R9" s="8" t="n">
         <v>56713</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="U9" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="V9" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>18985.5</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="X9" s="4" t="n">
         <v>1704.24</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="Y9" s="4" t="n">
         <v>57898.63</v>
       </c>
-      <c r="W9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>35925.48</v>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="AA9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Annual</t>
+      <c r="AB9" s="8" t="n">
+        <v>46182</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0 - Active</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="n">
+        <v>282011.38</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>GPT</t>
         </is>
       </c>
     </row>
@@ -4754,9 +4951,10 @@
       <c r="G169" s="2" t="n"/>
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="2" t="n"/>
-      <c r="M169" s="2" t="n"/>
+      <c r="J169" s="2" t="n"/>
       <c r="N169" s="2" t="n"/>
       <c r="O169" s="2" t="n"/>
+      <c r="P169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -4782,9 +4980,10 @@
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
-      <c r="M170" s="2" t="n"/>
+      <c r="J170" s="2" t="n"/>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="2" t="n"/>
+      <c r="P170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -4810,9 +5009,10 @@
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
-      <c r="M171" s="2" t="n"/>
+      <c r="J171" s="2" t="n"/>
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="2" t="n"/>
+      <c r="P171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -4882,9 +5082,10 @@
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="n"/>
-      <c r="M174" s="2" t="n"/>
+      <c r="J174" s="2" t="n"/>
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="2" t="n"/>
+      <c r="P174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -5218,9 +5419,10 @@
       <c r="G189" s="2" t="n"/>
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="n"/>
-      <c r="M189" s="2" t="n"/>
+      <c r="J189" s="2" t="n"/>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="2" t="n"/>
+      <c r="P189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -5444,9 +5646,10 @@
       <c r="G199" s="2" t="n"/>
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="2" t="n"/>
-      <c r="M199" s="2" t="n"/>
+      <c r="J199" s="2" t="n"/>
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="2" t="n"/>
+      <c r="P199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -5538,9 +5741,10 @@
       <c r="G203" s="2" t="n"/>
       <c r="H203" s="2" t="n"/>
       <c r="I203" s="2" t="n"/>
-      <c r="M203" s="2" t="n"/>
+      <c r="J203" s="2" t="n"/>
       <c r="N203" s="2" t="n"/>
       <c r="O203" s="2" t="n"/>
+      <c r="P203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -5720,9 +5924,10 @@
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
       <c r="I211" s="2" t="n"/>
-      <c r="M211" s="2" t="n"/>
+      <c r="J211" s="2" t="n"/>
       <c r="N211" s="2" t="n"/>
       <c r="O211" s="2" t="n"/>
+      <c r="P211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -5836,9 +6041,10 @@
       <c r="G216" s="2" t="n"/>
       <c r="H216" s="2" t="n"/>
       <c r="I216" s="2" t="n"/>
-      <c r="M216" s="2" t="n"/>
+      <c r="J216" s="2" t="n"/>
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="2" t="n"/>
+      <c r="P216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -5930,9 +6136,10 @@
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
       <c r="I220" s="2" t="n"/>
-      <c r="M220" s="2" t="n"/>
+      <c r="J220" s="2" t="n"/>
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="2" t="n"/>
+      <c r="P220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -5958,9 +6165,10 @@
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
       <c r="I221" s="2" t="n"/>
-      <c r="M221" s="2" t="n"/>
+      <c r="J221" s="2" t="n"/>
       <c r="N221" s="2" t="n"/>
       <c r="O221" s="2" t="n"/>
+      <c r="P221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -6074,9 +6282,10 @@
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
       <c r="I226" s="2" t="n"/>
-      <c r="M226" s="2" t="n"/>
+      <c r="J226" s="2" t="n"/>
       <c r="N226" s="2" t="n"/>
       <c r="O226" s="2" t="n"/>
+      <c r="P226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -6190,9 +6399,10 @@
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
       <c r="I231" s="2" t="n"/>
-      <c r="M231" s="2" t="n"/>
+      <c r="J231" s="2" t="n"/>
       <c r="N231" s="2" t="n"/>
       <c r="O231" s="2" t="n"/>
+      <c r="P231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
@@ -6218,9 +6428,10 @@
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
       <c r="I232" s="2" t="n"/>
-      <c r="M232" s="2" t="n"/>
+      <c r="J232" s="2" t="n"/>
       <c r="N232" s="2" t="n"/>
       <c r="O232" s="2" t="n"/>
+      <c r="P232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -6312,9 +6523,10 @@
       <c r="G236" s="2" t="n"/>
       <c r="H236" s="2" t="n"/>
       <c r="I236" s="2" t="n"/>
-      <c r="M236" s="2" t="n"/>
+      <c r="J236" s="2" t="n"/>
       <c r="N236" s="2" t="n"/>
       <c r="O236" s="2" t="n"/>
+      <c r="P236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -6384,9 +6596,10 @@
       <c r="G239" s="2" t="n"/>
       <c r="H239" s="2" t="n"/>
       <c r="I239" s="2" t="n"/>
-      <c r="M239" s="2" t="n"/>
+      <c r="J239" s="2" t="n"/>
       <c r="N239" s="2" t="n"/>
       <c r="O239" s="2" t="n"/>
+      <c r="P239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -6456,9 +6669,10 @@
       <c r="G242" s="2" t="n"/>
       <c r="H242" s="2" t="n"/>
       <c r="I242" s="2" t="n"/>
-      <c r="M242" s="2" t="n"/>
+      <c r="J242" s="2" t="n"/>
       <c r="N242" s="2" t="n"/>
       <c r="O242" s="2" t="n"/>
+      <c r="P242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -6638,9 +6852,10 @@
       <c r="G250" s="2" t="n"/>
       <c r="H250" s="2" t="n"/>
       <c r="I250" s="2" t="n"/>
-      <c r="M250" s="2" t="n"/>
+      <c r="J250" s="2" t="n"/>
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="2" t="n"/>
+      <c r="P250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -6666,9 +6881,10 @@
       <c r="G251" s="2" t="n"/>
       <c r="H251" s="2" t="n"/>
       <c r="I251" s="2" t="n"/>
-      <c r="M251" s="2" t="n"/>
+      <c r="J251" s="2" t="n"/>
       <c r="N251" s="2" t="n"/>
       <c r="O251" s="2" t="n"/>
+      <c r="P251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -6694,9 +6910,10 @@
       <c r="G252" s="2" t="n"/>
       <c r="H252" s="2" t="n"/>
       <c r="I252" s="2" t="n"/>
-      <c r="M252" s="2" t="n"/>
+      <c r="J252" s="2" t="n"/>
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="2" t="n"/>
+      <c r="P252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -6788,9 +7005,10 @@
       <c r="G256" s="2" t="n"/>
       <c r="H256" s="2" t="n"/>
       <c r="I256" s="2" t="n"/>
-      <c r="M256" s="2" t="n"/>
+      <c r="J256" s="2" t="n"/>
       <c r="N256" s="2" t="n"/>
       <c r="O256" s="2" t="n"/>
+      <c r="P256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -6882,9 +7100,10 @@
       <c r="G260" s="2" t="n"/>
       <c r="H260" s="2" t="n"/>
       <c r="I260" s="2" t="n"/>
-      <c r="M260" s="2" t="n"/>
+      <c r="J260" s="2" t="n"/>
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="2" t="n"/>
+      <c r="P260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -6910,9 +7129,10 @@
       <c r="G261" s="2" t="n"/>
       <c r="H261" s="2" t="n"/>
       <c r="I261" s="2" t="n"/>
-      <c r="M261" s="2" t="n"/>
+      <c r="J261" s="2" t="n"/>
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="2" t="n"/>
+      <c r="P261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -7070,9 +7290,10 @@
       <c r="G268" s="2" t="n"/>
       <c r="H268" s="2" t="n"/>
       <c r="I268" s="2" t="n"/>
-      <c r="M268" s="2" t="n"/>
+      <c r="J268" s="2" t="n"/>
       <c r="N268" s="2" t="n"/>
       <c r="O268" s="2" t="n"/>
+      <c r="P268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -7120,9 +7341,10 @@
       <c r="G270" s="2" t="n"/>
       <c r="H270" s="2" t="n"/>
       <c r="I270" s="2" t="n"/>
-      <c r="M270" s="2" t="n"/>
+      <c r="J270" s="2" t="n"/>
       <c r="N270" s="2" t="n"/>
       <c r="O270" s="2" t="n"/>
+      <c r="P270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -7236,9 +7458,10 @@
       <c r="G275" s="2" t="n"/>
       <c r="H275" s="2" t="n"/>
       <c r="I275" s="2" t="n"/>
-      <c r="M275" s="2" t="n"/>
+      <c r="J275" s="2" t="n"/>
       <c r="N275" s="2" t="n"/>
       <c r="O275" s="2" t="n"/>
+      <c r="P275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -7374,9 +7597,10 @@
       <c r="G281" s="2" t="n"/>
       <c r="H281" s="2" t="n"/>
       <c r="I281" s="2" t="n"/>
-      <c r="M281" s="2" t="n"/>
+      <c r="J281" s="2" t="n"/>
       <c r="N281" s="2" t="n"/>
       <c r="O281" s="2" t="n"/>
+      <c r="P281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -7776,9 +8000,10 @@
       <c r="G299" s="2" t="n"/>
       <c r="H299" s="2" t="n"/>
       <c r="I299" s="2" t="n"/>
-      <c r="M299" s="2" t="n"/>
+      <c r="J299" s="2" t="n"/>
       <c r="N299" s="2" t="n"/>
       <c r="O299" s="2" t="n"/>
+      <c r="P299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -8222,9 +8447,10 @@
       <c r="G319" s="2" t="n"/>
       <c r="H319" s="2" t="n"/>
       <c r="I319" s="2" t="n"/>
-      <c r="M319" s="2" t="n"/>
+      <c r="J319" s="2" t="n"/>
       <c r="N319" s="2" t="n"/>
       <c r="O319" s="2" t="n"/>
+      <c r="P319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
@@ -8382,9 +8608,10 @@
       <c r="G326" s="2" t="n"/>
       <c r="H326" s="2" t="n"/>
       <c r="I326" s="2" t="n"/>
-      <c r="M326" s="2" t="n"/>
+      <c r="J326" s="2" t="n"/>
       <c r="N326" s="2" t="n"/>
       <c r="O326" s="2" t="n"/>
+      <c r="P326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -8520,9 +8747,10 @@
       <c r="G332" s="2" t="n"/>
       <c r="H332" s="2" t="n"/>
       <c r="I332" s="2" t="n"/>
-      <c r="M332" s="2" t="n"/>
+      <c r="J332" s="2" t="n"/>
       <c r="N332" s="2" t="n"/>
       <c r="O332" s="2" t="n"/>
+      <c r="P332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
